--- a/data_monthly.xlsx
+++ b/data_monthly.xlsx
@@ -852,7 +852,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,12 +864,6 @@
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1437,7 +1431,7 @@
       <c r="B2" s="2">
         <v>2182916966</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>14916132.75</v>
       </c>
       <c r="D2" s="3">
@@ -1454,7 +1448,7 @@
       <c r="B3" s="2">
         <v>2153790143</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>16573151.5</v>
       </c>
       <c r="D3" s="3">
@@ -1471,7 +1465,7 @@
       <c r="B4" s="2">
         <v>2546013172</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>18241385.2</v>
       </c>
       <c r="D4" s="3">
@@ -1488,7 +1482,7 @@
       <c r="B5" s="2">
         <v>2519076701</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>20230772.25</v>
       </c>
       <c r="D5" s="3">
@@ -1505,7 +1499,7 @@
       <c r="B6" s="2">
         <v>2758906073</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>21353074</v>
       </c>
       <c r="D6" s="3">
@@ -1522,7 +1516,7 @@
       <c r="B7" s="2">
         <v>2858428807</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>22705036.8</v>
       </c>
       <c r="D7" s="3">
@@ -1539,7 +1533,7 @@
       <c r="B8" s="2">
         <v>3077548077</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>24494982.75</v>
       </c>
       <c r="D8" s="3">
@@ -1556,7 +1550,7 @@
       <c r="B9" s="2">
         <v>3278230437</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>25704015</v>
       </c>
       <c r="D9" s="3">
@@ -1573,7 +1567,7 @@
       <c r="B10" s="2">
         <v>3351055742</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>27004151.6</v>
       </c>
       <c r="D10" s="3">
@@ -1590,7 +1584,7 @@
       <c r="B11" s="2">
         <v>3554608720</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>27431284.25</v>
       </c>
       <c r="D11" s="3">
@@ -1607,7 +1601,7 @@
       <c r="B12" s="2">
         <v>3705354264</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>27771731</v>
       </c>
       <c r="D12" s="3">
@@ -1624,7 +1618,7 @@
       <c r="B13" s="2">
         <v>4213424368</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>27543626.2</v>
       </c>
       <c r="D13" s="3">
@@ -1641,7 +1635,7 @@
       <c r="B14" s="2">
         <v>3850642790</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>28135278.25</v>
       </c>
       <c r="D14" s="3">
@@ -1658,7 +1652,7 @@
       <c r="B15" s="2">
         <v>3847081494</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>28968112</v>
       </c>
       <c r="D15" s="3">
@@ -1675,7 +1669,7 @@
       <c r="B16" s="2">
         <v>4322927194</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
         <v>29763145.8</v>
       </c>
       <c r="D16" s="3">
@@ -1692,7 +1686,7 @@
       <c r="B17" s="2">
         <v>4345270379</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="4">
         <v>30274134.25</v>
       </c>
       <c r="D17" s="3">
@@ -1709,7 +1703,7 @@
       <c r="B18" s="2">
         <v>4620740116</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="4">
         <v>29386495.2</v>
       </c>
       <c r="D18" s="3">
@@ -1726,7 +1720,7 @@
       <c r="B19" s="2">
         <v>4657223835</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="4">
         <v>30358426</v>
       </c>
       <c r="D19" s="3">
@@ -1743,7 +1737,7 @@
       <c r="B20" s="2">
         <v>4786637559</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="4">
         <v>31682428.25</v>
       </c>
       <c r="D20" s="3">
@@ -1760,7 +1754,7 @@
       <c r="B21" s="2">
         <v>5009383921</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="4">
         <v>32971656.4</v>
       </c>
       <c r="D21" s="3">
@@ -1777,7 +1771,7 @@
       <c r="B22" s="2">
         <v>4894958645</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="4">
         <v>34685834.75</v>
       </c>
       <c r="D22" s="3">
@@ -1794,7 +1788,7 @@
       <c r="B23" s="2">
         <v>5096156670</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="4">
         <v>36432989.5</v>
       </c>
       <c r="D23" s="3">
@@ -1811,7 +1805,7 @@
       <c r="B24" s="2">
         <v>5171276538</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="4">
         <v>38554629.4</v>
       </c>
       <c r="D24" s="3">
@@ -1828,7 +1822,7 @@
       <c r="B25" s="2">
         <v>5710113496</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="4">
         <v>40571953.25</v>
       </c>
       <c r="D25" s="3">
@@ -1845,7 +1839,7 @@
       <c r="B26" s="2">
         <v>5060285434</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="4">
         <v>42751539</v>
       </c>
       <c r="D26" s="3">
@@ -1862,7 +1856,7 @@
       <c r="B27" s="2">
         <v>4985804933</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="4">
         <v>44715926</v>
       </c>
       <c r="D27" s="3">
@@ -1879,7 +1873,7 @@
       <c r="B28" s="2">
         <v>5564431400</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="4">
         <v>48324762.25</v>
       </c>
       <c r="D28" s="3">
@@ -1896,7 +1890,7 @@
       <c r="B29" s="2">
         <v>5598161245</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="4">
         <v>51414088</v>
       </c>
       <c r="D29" s="3">
@@ -1913,7 +1907,7 @@
       <c r="B30" s="2">
         <v>5930140613</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="4">
         <v>54324901.4</v>
       </c>
       <c r="D30" s="3">
@@ -1930,7 +1924,7 @@
       <c r="B31" s="2">
         <v>5799009959</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="4">
         <v>58980086.25</v>
       </c>
       <c r="D31" s="3">
@@ -1947,7 +1941,7 @@
       <c r="B32" s="2">
         <v>5996860799</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="4">
         <v>62406312</v>
       </c>
       <c r="D32" s="3">
@@ -1964,7 +1958,7 @@
       <c r="B33" s="2">
         <v>6239608083</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="4">
         <v>66675128.4</v>
       </c>
       <c r="D33" s="3">
@@ -1981,7 +1975,7 @@
       <c r="B34" s="2">
         <v>6133276456</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="4">
         <v>71225378</v>
       </c>
       <c r="D34" s="3">
@@ -1998,7 +1992,7 @@
       <c r="B35" s="2">
         <v>6453005306</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="4">
         <v>81134686.4</v>
       </c>
       <c r="D35" s="3">
@@ -2015,7 +2009,7 @@
       <c r="B36" s="2">
         <v>6460898394</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="4">
         <v>89628538.75</v>
       </c>
       <c r="D36" s="3">
@@ -2032,7 +2026,7 @@
       <c r="B37" s="2">
         <v>7098633064</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="4">
         <v>97846458.5</v>
       </c>
       <c r="D37" s="3">
@@ -2051,8 +2045,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E72"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="4" width="18.6923076923077" customWidth="1"/>
   </cols>
@@ -2939,65 +2933,6 @@
         <v>107.23992</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="B64" s="4"/>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
